--- a/job_application_forms/024_financial_advisor_job_application_form--job_application_forms.xlsx
+++ b/job_application_forms/024_financial_advisor_job_application_form--job_application_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Label</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone Label</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Address Label</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title Label</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>employment_type</t>
+          <t>Employment Type Label</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Employment Status</t>
+          <t>Employment Status Label</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Job Type</t>
+          <t>Job Type Label</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Employment Status Details</t>
+          <t>Employment Status Details Label</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Employment History Years</t>
+          <t>Employment History Years Label</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
